--- a/output_tables/p_gps_pts1_groupno.xlsx
+++ b/output_tables/p_gps_pts1_groupno.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofwa-my.sharepoint.com/personal/peter_dowty_dnr_wa_gov/Documents/projects/seagrass_restoration_data_2026/output_tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="8_{8D93D302-86F1-4BDE-BA85-C1D4E21B1AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D58863E5-E841-429E-A0BE-0A8319D87745}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{8D93D302-86F1-4BDE-BA85-C1D4E21B1AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F2EE461-A478-4187-A2DC-EF3BA74EE8DE}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="105" windowWidth="28785" windowHeight="15390" xr2:uid="{308FDB03-57E4-4B58-ADF4-6D420AFE65D3}"/>
+    <workbookView xWindow="75" yWindow="75" windowWidth="28785" windowHeight="15390" xr2:uid="{308FDB03-57E4-4B58-ADF4-6D420AFE65D3}"/>
   </bookViews>
   <sheets>
     <sheet name="p_gps_pts1_groupno" sheetId="1" r:id="rId1"/>
@@ -2309,7 +2309,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2507,6 +2507,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="12">
     <border>
@@ -2694,14 +2700,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2711,6 +2716,8 @@
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3223,19 +3230,19 @@
       <c r="AE1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AG1" s="10" t="s">
         <v>694</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AH1" s="10" t="s">
         <v>695</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AI1" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>697</v>
       </c>
     </row>
@@ -3340,7 +3347,7 @@
         <f>COUNTIF(AF:AF,AF2)</f>
         <v>1</v>
       </c>
-      <c r="AH2" s="6" t="str">
+      <c r="AH2" s="5" t="str">
         <f>IF(AG2&gt;1,AF2,"")</f>
         <v/>
       </c>
@@ -3454,7 +3461,7 @@
         <f t="shared" ref="AG3:AG66" si="0">COUNTIF(AF:AF,AF3)</f>
         <v>1</v>
       </c>
-      <c r="AH3" s="6" t="str">
+      <c r="AH3" s="5" t="str">
         <f t="shared" ref="AH3:AH66" si="1">IF(AG3&gt;1,AF3,"")</f>
         <v/>
       </c>
@@ -3568,7 +3575,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH4" s="6" t="str">
+      <c r="AH4" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3682,7 +3689,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH5" s="6" t="str">
+      <c r="AH5" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3796,7 +3803,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH6" s="6" t="str">
+      <c r="AH6" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3910,7 +3917,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH7" s="6">
+      <c r="AH7" s="5">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -4027,7 +4034,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH8" s="6">
+      <c r="AH8" s="5">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -4144,7 +4151,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH9" s="6">
+      <c r="AH9" s="5">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
@@ -4261,7 +4268,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH10" s="6">
+      <c r="AH10" s="5">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
@@ -4378,7 +4385,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH11" s="6">
+      <c r="AH11" s="5">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
@@ -4495,7 +4502,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH12" s="6">
+      <c r="AH12" s="5">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
@@ -4612,7 +4619,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH13" s="6">
+      <c r="AH13" s="5">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
@@ -4729,7 +4736,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH14" s="6">
+      <c r="AH14" s="5">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
@@ -4846,7 +4853,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH15" s="6">
+      <c r="AH15" s="5">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -4963,7 +4970,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH16" s="6">
+      <c r="AH16" s="5">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -5080,7 +5087,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH17" s="6" t="str">
+      <c r="AH17" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -5194,7 +5201,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH18" s="6" t="str">
+      <c r="AH18" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -5308,7 +5315,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH19" s="6" t="str">
+      <c r="AH19" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -5422,7 +5429,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH20" s="6" t="str">
+      <c r="AH20" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -5536,7 +5543,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH21" s="6" t="str">
+      <c r="AH21" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -5650,7 +5657,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH22" s="6" t="str">
+      <c r="AH22" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -5764,7 +5771,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH23" s="6" t="str">
+      <c r="AH23" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -5878,7 +5885,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH24" s="6" t="str">
+      <c r="AH24" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -5886,7 +5893,7 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="AJ24" s="7" t="str">
+      <c r="AJ24" s="6" t="str">
         <f t="shared" si="3"/>
         <v>BB_test_1</v>
       </c>
@@ -5998,7 +6005,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH25" s="6" t="str">
+      <c r="AH25" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6006,7 +6013,7 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="AJ25" s="7" t="str">
+      <c r="AJ25" s="6" t="str">
         <f t="shared" si="3"/>
         <v>BB_test_1</v>
       </c>
@@ -6115,7 +6122,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH26" s="6" t="str">
+      <c r="AH26" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6123,7 +6130,7 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="AJ26" s="7" t="str">
+      <c r="AJ26" s="6" t="str">
         <f t="shared" si="3"/>
         <v>BB_test_1</v>
       </c>
@@ -6232,7 +6239,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH27" s="6" t="str">
+      <c r="AH27" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6240,7 +6247,7 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="AJ27" s="7" t="str">
+      <c r="AJ27" s="6" t="str">
         <f t="shared" si="3"/>
         <v>BB_test_1</v>
       </c>
@@ -6333,7 +6340,7 @@
       <c r="AB28">
         <v>100</v>
       </c>
-      <c r="AC28" t="s">
+      <c r="AC28" s="8" t="s">
         <v>120</v>
       </c>
       <c r="AD28" t="s">
@@ -6349,7 +6356,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH28" s="6" t="str">
+      <c r="AH28" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6357,7 +6364,7 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="AJ28" s="7" t="str">
+      <c r="AJ28" s="6" t="str">
         <f t="shared" si="3"/>
         <v>BB_test_1</v>
       </c>
@@ -6466,7 +6473,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH29" s="6" t="str">
+      <c r="AH29" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6580,7 +6587,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH30" s="6" t="str">
+      <c r="AH30" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6694,7 +6701,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH31" s="6" t="str">
+      <c r="AH31" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6808,7 +6815,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH32" s="6">
+      <c r="AH32" s="5">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
@@ -6925,7 +6932,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH33" s="6">
+      <c r="AH33" s="5">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
@@ -7042,7 +7049,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH34" s="6">
+      <c r="AH34" s="5">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
@@ -7159,7 +7166,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH35" s="6">
+      <c r="AH35" s="5">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
@@ -7276,7 +7283,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH36" s="6" t="str">
+      <c r="AH36" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -7284,7 +7291,7 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AJ36" s="7" t="str">
+      <c r="AJ36" s="6" t="str">
         <f t="shared" si="3"/>
         <v>DEL_1</v>
       </c>
@@ -7393,7 +7400,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH37" s="6">
+      <c r="AH37" s="5">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
@@ -7510,7 +7517,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH38" s="6">
+      <c r="AH38" s="5">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
@@ -7627,7 +7634,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="AH39" s="6">
+      <c r="AH39" s="5">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
@@ -7744,7 +7751,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="AH40" s="6">
+      <c r="AH40" s="5">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
@@ -7861,7 +7868,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="AH41" s="6">
+      <c r="AH41" s="5">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
@@ -7978,7 +7985,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="AH42" s="6">
+      <c r="AH42" s="5">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
@@ -8095,7 +8102,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH43" s="6" t="str">
+      <c r="AH43" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8103,7 +8110,7 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AJ43" s="7" t="str">
+      <c r="AJ43" s="6" t="str">
         <f t="shared" si="3"/>
         <v>DEL_3</v>
       </c>
@@ -8212,7 +8219,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH44" s="6" t="str">
+      <c r="AH44" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8326,7 +8333,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH45" s="6" t="str">
+      <c r="AH45" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8334,7 +8341,7 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AJ45" s="7" t="str">
+      <c r="AJ45" s="6" t="str">
         <f t="shared" si="3"/>
         <v>DEL_1</v>
       </c>
@@ -8443,7 +8450,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH46" s="6" t="str">
+      <c r="AH46" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8451,7 +8458,7 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AJ46" s="7" t="str">
+      <c r="AJ46" s="6" t="str">
         <f t="shared" si="3"/>
         <v>DEL_3</v>
       </c>
@@ -8560,7 +8567,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH47" s="6" t="str">
+      <c r="AH47" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8674,7 +8681,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH48" s="6" t="str">
+      <c r="AH48" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8788,7 +8795,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH49" s="6" t="str">
+      <c r="AH49" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8902,7 +8909,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH50" s="6" t="str">
+      <c r="AH50" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9016,7 +9023,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH51" s="6" t="str">
+      <c r="AH51" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9130,7 +9137,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH52" s="6" t="str">
+      <c r="AH52" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9244,7 +9251,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH53" s="6" t="str">
+      <c r="AH53" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9252,7 +9259,7 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="AJ53" s="7" t="str">
+      <c r="AJ53" s="6" t="str">
         <f t="shared" si="3"/>
         <v>DB_test_2</v>
       </c>
@@ -9364,7 +9371,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH54" s="6" t="str">
+      <c r="AH54" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9372,7 +9379,7 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="AJ54" s="7" t="str">
+      <c r="AJ54" s="6" t="str">
         <f t="shared" si="3"/>
         <v>DB_test_2</v>
       </c>
@@ -9481,7 +9488,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH55" s="6" t="str">
+      <c r="AH55" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9489,7 +9496,7 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="AJ55" s="7" t="str">
+      <c r="AJ55" s="6" t="str">
         <f t="shared" si="3"/>
         <v>DB_test_2</v>
       </c>
@@ -9598,7 +9605,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH56" s="6" t="str">
+      <c r="AH56" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9606,7 +9613,7 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="AJ56" s="7" t="str">
+      <c r="AJ56" s="6" t="str">
         <f t="shared" si="3"/>
         <v>DB_test_2</v>
       </c>
@@ -9715,7 +9722,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH57" s="6" t="str">
+      <c r="AH57" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9829,7 +9836,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH58" s="6" t="str">
+      <c r="AH58" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9943,7 +9950,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH59" s="6" t="str">
+      <c r="AH59" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10057,7 +10064,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH60" s="6" t="str">
+      <c r="AH60" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10171,7 +10178,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH61" s="6" t="str">
+      <c r="AH61" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10285,7 +10292,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH62" s="6" t="str">
+      <c r="AH62" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10399,7 +10406,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH63" s="6" t="str">
+      <c r="AH63" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10513,7 +10520,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH64" s="6" t="str">
+      <c r="AH64" s="5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10627,7 +10634,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH65" s="6">
+      <c r="AH65" s="5">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
@@ -10744,7 +10751,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="AH66" s="6">
+      <c r="AH66" s="5">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
@@ -10861,7 +10868,7 @@
         <f t="shared" ref="AG67:AG130" si="4">COUNTIF(AF:AF,AF67)</f>
         <v>2</v>
       </c>
-      <c r="AH67" s="6">
+      <c r="AH67" s="5">
         <f t="shared" ref="AH67:AH130" si="5">IF(AG67&gt;1,AF67,"")</f>
         <v>54</v>
       </c>
@@ -10978,7 +10985,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AH68" s="6">
+      <c r="AH68" s="5">
         <f t="shared" si="5"/>
         <v>54</v>
       </c>
@@ -11095,7 +11102,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AH69" s="6">
+      <c r="AH69" s="5">
         <f t="shared" si="5"/>
         <v>55</v>
       </c>
@@ -11212,7 +11219,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AH70" s="6">
+      <c r="AH70" s="5">
         <f t="shared" si="5"/>
         <v>55</v>
       </c>
@@ -11329,7 +11336,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AH71" s="6">
+      <c r="AH71" s="5">
         <f t="shared" si="5"/>
         <v>56</v>
       </c>
@@ -11446,7 +11453,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AH72" s="6">
+      <c r="AH72" s="5">
         <f t="shared" si="5"/>
         <v>56</v>
       </c>
@@ -11563,7 +11570,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH73" s="6" t="str">
+      <c r="AH73" s="5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -11677,7 +11684,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH74" s="6" t="str">
+      <c r="AH74" s="5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -11791,7 +11798,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH75" s="6" t="str">
+      <c r="AH75" s="5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -11905,7 +11912,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH76" s="6" t="str">
+      <c r="AH76" s="5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -12019,7 +12026,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH77" s="6" t="str">
+      <c r="AH77" s="5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -12027,7 +12034,7 @@
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="AJ77" s="7" t="str">
+      <c r="AJ77" s="6" t="str">
         <f t="shared" si="7"/>
         <v>HAR_4</v>
       </c>
@@ -12139,7 +12146,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH78" s="6" t="str">
+      <c r="AH78" s="5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -12147,7 +12154,7 @@
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="AJ78" s="7" t="str">
+      <c r="AJ78" s="6" t="str">
         <f t="shared" si="7"/>
         <v>HAR_4</v>
       </c>
@@ -12256,7 +12263,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH79" s="6" t="str">
+      <c r="AH79" s="5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -12370,7 +12377,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AH80" s="6">
+      <c r="AH80" s="5">
         <f t="shared" si="5"/>
         <v>64</v>
       </c>
@@ -12487,7 +12494,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AH81" s="6">
+      <c r="AH81" s="5">
         <f t="shared" si="5"/>
         <v>64</v>
       </c>
@@ -12604,7 +12611,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AH82" s="6">
+      <c r="AH82" s="5">
         <f t="shared" si="5"/>
         <v>65</v>
       </c>
@@ -12721,7 +12728,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AH83" s="6">
+      <c r="AH83" s="5">
         <f t="shared" si="5"/>
         <v>65</v>
       </c>
@@ -12838,7 +12845,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AH84" s="6">
+      <c r="AH84" s="5">
         <f t="shared" si="5"/>
         <v>66</v>
       </c>
@@ -12955,7 +12962,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AH85" s="6">
+      <c r="AH85" s="5">
         <f t="shared" si="5"/>
         <v>66</v>
       </c>
@@ -13072,7 +13079,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AH86" s="6">
+      <c r="AH86" s="5">
         <f t="shared" si="5"/>
         <v>67</v>
       </c>
@@ -13189,7 +13196,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AH87" s="6">
+      <c r="AH87" s="5">
         <f t="shared" si="5"/>
         <v>67</v>
       </c>
@@ -13306,7 +13313,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH88" s="6" t="str">
+      <c r="AH88" s="5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -13420,7 +13427,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH89" s="6" t="str">
+      <c r="AH89" s="5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -13534,7 +13541,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH90" s="6" t="str">
+      <c r="AH90" s="5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -13648,7 +13655,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH91" s="6" t="str">
+      <c r="AH91" s="5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -13762,7 +13769,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH92" s="6" t="str">
+      <c r="AH92" s="5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -13770,7 +13777,7 @@
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="AJ92" s="7" t="str">
+      <c r="AJ92" s="6" t="str">
         <f t="shared" si="7"/>
         <v>HPT_north_2</v>
       </c>
@@ -13879,7 +13886,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH93" s="6" t="str">
+      <c r="AH93" s="5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -13993,7 +14000,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH94" s="6" t="str">
+      <c r="AH94" s="5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -14001,7 +14008,7 @@
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="AJ94" s="7" t="str">
+      <c r="AJ94" s="6" t="str">
         <f t="shared" si="7"/>
         <v>HPT_north_2</v>
       </c>
@@ -14113,7 +14120,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH95" s="6" t="str">
+      <c r="AH95" s="5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -14227,7 +14234,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH96" s="6" t="str">
+      <c r="AH96" s="5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -14341,7 +14348,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH97" s="6">
+      <c r="AH97" s="5">
         <f t="shared" si="5"/>
         <v>77</v>
       </c>
@@ -14458,7 +14465,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH98" s="6">
+      <c r="AH98" s="5">
         <f t="shared" si="5"/>
         <v>77</v>
       </c>
@@ -14575,7 +14582,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH99" s="6">
+      <c r="AH99" s="5">
         <f t="shared" si="5"/>
         <v>77</v>
       </c>
@@ -14692,7 +14699,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH100" s="6">
+      <c r="AH100" s="5">
         <f t="shared" si="5"/>
         <v>77</v>
       </c>
@@ -14809,7 +14816,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH101" s="6">
+      <c r="AH101" s="5">
         <f t="shared" si="5"/>
         <v>78</v>
       </c>
@@ -14926,7 +14933,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH102" s="6">
+      <c r="AH102" s="5">
         <f t="shared" si="5"/>
         <v>78</v>
       </c>
@@ -15043,7 +15050,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH103" s="6">
+      <c r="AH103" s="5">
         <f t="shared" si="5"/>
         <v>78</v>
       </c>
@@ -15160,7 +15167,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH104" s="6">
+      <c r="AH104" s="5">
         <f t="shared" si="5"/>
         <v>78</v>
       </c>
@@ -15277,7 +15284,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH105" s="6" t="str">
+      <c r="AH105" s="5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -15391,7 +15398,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AH106" s="6">
+      <c r="AH106" s="5">
         <f t="shared" si="5"/>
         <v>80</v>
       </c>
@@ -15508,7 +15515,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AH107" s="6">
+      <c r="AH107" s="5">
         <f t="shared" si="5"/>
         <v>80</v>
       </c>
@@ -15625,7 +15632,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH108" s="6">
+      <c r="AH108" s="5">
         <f t="shared" si="5"/>
         <v>81</v>
       </c>
@@ -15742,7 +15749,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH109" s="6">
+      <c r="AH109" s="5">
         <f t="shared" si="5"/>
         <v>81</v>
       </c>
@@ -15859,7 +15866,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH110" s="6">
+      <c r="AH110" s="5">
         <f t="shared" si="5"/>
         <v>81</v>
       </c>
@@ -15976,7 +15983,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH111" s="6">
+      <c r="AH111" s="5">
         <f t="shared" si="5"/>
         <v>81</v>
       </c>
@@ -16093,7 +16100,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH112" s="6" t="str">
+      <c r="AH112" s="5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -16207,7 +16214,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AH113" s="6">
+      <c r="AH113" s="5">
         <f t="shared" si="5"/>
         <v>83</v>
       </c>
@@ -16324,7 +16331,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AH114" s="6">
+      <c r="AH114" s="5">
         <f t="shared" si="5"/>
         <v>83</v>
       </c>
@@ -16441,7 +16448,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AH115" s="6">
+      <c r="AH115" s="5">
         <f t="shared" si="5"/>
         <v>84</v>
       </c>
@@ -16558,7 +16565,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AH116" s="6">
+      <c r="AH116" s="5">
         <f t="shared" si="5"/>
         <v>84</v>
       </c>
@@ -16675,7 +16682,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH117" s="6">
+      <c r="AH117" s="5">
         <f t="shared" si="5"/>
         <v>85</v>
       </c>
@@ -16792,7 +16799,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH118" s="6">
+      <c r="AH118" s="5">
         <f t="shared" si="5"/>
         <v>85</v>
       </c>
@@ -16909,7 +16916,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH119" s="6">
+      <c r="AH119" s="5">
         <f t="shared" si="5"/>
         <v>85</v>
       </c>
@@ -17026,7 +17033,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH120" s="6">
+      <c r="AH120" s="5">
         <f t="shared" si="5"/>
         <v>85</v>
       </c>
@@ -17143,7 +17150,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH121" s="6">
+      <c r="AH121" s="5">
         <f t="shared" si="5"/>
         <v>86</v>
       </c>
@@ -17260,7 +17267,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH122" s="6">
+      <c r="AH122" s="5">
         <f t="shared" si="5"/>
         <v>86</v>
       </c>
@@ -17377,7 +17384,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH123" s="6">
+      <c r="AH123" s="5">
         <f t="shared" si="5"/>
         <v>86</v>
       </c>
@@ -17494,7 +17501,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH124" s="6">
+      <c r="AH124" s="5">
         <f t="shared" si="5"/>
         <v>86</v>
       </c>
@@ -17611,7 +17618,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH125" s="6">
+      <c r="AH125" s="5">
         <f t="shared" si="5"/>
         <v>87</v>
       </c>
@@ -17728,7 +17735,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH126" s="6">
+      <c r="AH126" s="5">
         <f t="shared" si="5"/>
         <v>87</v>
       </c>
@@ -17845,7 +17852,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH127" s="6">
+      <c r="AH127" s="5">
         <f t="shared" si="5"/>
         <v>87</v>
       </c>
@@ -17962,7 +17969,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AH128" s="6">
+      <c r="AH128" s="5">
         <f t="shared" si="5"/>
         <v>87</v>
       </c>
@@ -18079,7 +18086,7 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="AH129" s="6">
+      <c r="AH129" s="5">
         <f t="shared" si="5"/>
         <v>88</v>
       </c>
@@ -18091,7 +18098,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK129" s="8" t="s">
+      <c r="AK129" s="7" t="s">
         <v>703</v>
       </c>
     </row>
@@ -18196,7 +18203,7 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="AH130" s="6">
+      <c r="AH130" s="5">
         <f t="shared" si="5"/>
         <v>88</v>
       </c>
@@ -18208,7 +18215,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AK130" s="8"/>
+      <c r="AK130" s="7"/>
     </row>
     <row r="131" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131">
@@ -18311,7 +18318,7 @@
         <f t="shared" ref="AG131:AG194" si="8">COUNTIF(AF:AF,AF131)</f>
         <v>12</v>
       </c>
-      <c r="AH131" s="6">
+      <c r="AH131" s="5">
         <f t="shared" ref="AH131:AH194" si="9">IF(AG131&gt;1,AF131,"")</f>
         <v>88</v>
       </c>
@@ -18323,7 +18330,7 @@
         <f t="shared" ref="AJ131:AJ194" si="11">IF(AI131&gt;1,D131,"")</f>
         <v/>
       </c>
-      <c r="AK131" s="8"/>
+      <c r="AK131" s="7"/>
     </row>
     <row r="132" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132">
@@ -18426,7 +18433,7 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="AH132" s="6">
+      <c r="AH132" s="5">
         <f t="shared" si="9"/>
         <v>88</v>
       </c>
@@ -18438,7 +18445,7 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AK132" s="8"/>
+      <c r="AK132" s="7"/>
     </row>
     <row r="133" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133">
@@ -18541,7 +18548,7 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="AH133" s="6">
+      <c r="AH133" s="5">
         <f t="shared" si="9"/>
         <v>88</v>
       </c>
@@ -18553,7 +18560,7 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AK133" s="8"/>
+      <c r="AK133" s="7"/>
     </row>
     <row r="134" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134">
@@ -18656,7 +18663,7 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="AH134" s="6">
+      <c r="AH134" s="5">
         <f t="shared" si="9"/>
         <v>88</v>
       </c>
@@ -18668,7 +18675,7 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AK134" s="8"/>
+      <c r="AK134" s="7"/>
     </row>
     <row r="135" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135">
@@ -18771,7 +18778,7 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="AH135" s="6">
+      <c r="AH135" s="5">
         <f t="shared" si="9"/>
         <v>88</v>
       </c>
@@ -18783,7 +18790,7 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AK135" s="8"/>
+      <c r="AK135" s="7"/>
     </row>
     <row r="136" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136">
@@ -18886,7 +18893,7 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="AH136" s="6">
+      <c r="AH136" s="5">
         <f t="shared" si="9"/>
         <v>88</v>
       </c>
@@ -18898,7 +18905,7 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AK136" s="8"/>
+      <c r="AK136" s="7"/>
     </row>
     <row r="137" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137">
@@ -19001,7 +19008,7 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="AH137" s="6">
+      <c r="AH137" s="5">
         <f t="shared" si="9"/>
         <v>88</v>
       </c>
@@ -19013,7 +19020,7 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AK137" s="8"/>
+      <c r="AK137" s="7"/>
     </row>
     <row r="138" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138">
@@ -19116,7 +19123,7 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="AH138" s="6">
+      <c r="AH138" s="5">
         <f t="shared" si="9"/>
         <v>88</v>
       </c>
@@ -19128,7 +19135,7 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AK138" s="8"/>
+      <c r="AK138" s="7"/>
     </row>
     <row r="139" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139">
@@ -19231,7 +19238,7 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="AH139" s="6">
+      <c r="AH139" s="5">
         <f t="shared" si="9"/>
         <v>88</v>
       </c>
@@ -19243,7 +19250,7 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AK139" s="8"/>
+      <c r="AK139" s="7"/>
     </row>
     <row r="140" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140">
@@ -19346,7 +19353,7 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="AH140" s="6">
+      <c r="AH140" s="5">
         <f t="shared" si="9"/>
         <v>88</v>
       </c>
@@ -19358,7 +19365,7 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AK140" s="8"/>
+      <c r="AK140" s="7"/>
     </row>
     <row r="141" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141">
@@ -19367,7 +19374,7 @@
       <c r="B141" t="s">
         <v>291</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C141" s="6" t="s">
         <v>384</v>
       </c>
       <c r="D141" t="s">
@@ -19461,7 +19468,7 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="AH141" s="6">
+      <c r="AH141" s="5">
         <f t="shared" si="9"/>
         <v>89</v>
       </c>
@@ -19484,7 +19491,7 @@
       <c r="B142" t="s">
         <v>291</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C142" s="6" t="s">
         <v>388</v>
       </c>
       <c r="D142" t="s">
@@ -19578,7 +19585,7 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="AH142" s="6">
+      <c r="AH142" s="5">
         <f t="shared" si="9"/>
         <v>89</v>
       </c>
@@ -19601,7 +19608,7 @@
       <c r="B143" t="s">
         <v>291</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C143" s="6" t="s">
         <v>390</v>
       </c>
       <c r="D143" t="s">
@@ -19695,7 +19702,7 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="AH143" s="6">
+      <c r="AH143" s="5">
         <f t="shared" si="9"/>
         <v>89</v>
       </c>
@@ -19718,7 +19725,7 @@
       <c r="B144" t="s">
         <v>291</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C144" s="6" t="s">
         <v>391</v>
       </c>
       <c r="D144" t="s">
@@ -19812,7 +19819,7 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="AH144" s="6">
+      <c r="AH144" s="5">
         <f t="shared" si="9"/>
         <v>89</v>
       </c>
@@ -19835,7 +19842,7 @@
       <c r="B145" t="s">
         <v>291</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C145" s="6" t="s">
         <v>392</v>
       </c>
       <c r="D145" t="s">
@@ -19929,7 +19936,7 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="AH145" s="6">
+      <c r="AH145" s="5">
         <f t="shared" si="9"/>
         <v>90</v>
       </c>
@@ -19952,7 +19959,7 @@
       <c r="B146" t="s">
         <v>291</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C146" s="6" t="s">
         <v>394</v>
       </c>
       <c r="D146" t="s">
@@ -20046,7 +20053,7 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="AH146" s="6">
+      <c r="AH146" s="5">
         <f t="shared" si="9"/>
         <v>90</v>
       </c>
@@ -20069,7 +20076,7 @@
       <c r="B147" t="s">
         <v>291</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C147" s="6" t="s">
         <v>395</v>
       </c>
       <c r="D147" t="s">
@@ -20163,7 +20170,7 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="AH147" s="6">
+      <c r="AH147" s="5">
         <f t="shared" si="9"/>
         <v>90</v>
       </c>
@@ -20186,7 +20193,7 @@
       <c r="B148" t="s">
         <v>291</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C148" s="6" t="s">
         <v>396</v>
       </c>
       <c r="D148" t="s">
@@ -20280,7 +20287,7 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="AH148" s="6">
+      <c r="AH148" s="5">
         <f t="shared" si="9"/>
         <v>90</v>
       </c>
@@ -20303,7 +20310,7 @@
       <c r="B149" t="s">
         <v>291</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C149" s="6" t="s">
         <v>397</v>
       </c>
       <c r="D149" t="s">
@@ -20397,7 +20404,7 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="AH149" s="6">
+      <c r="AH149" s="5">
         <f t="shared" si="9"/>
         <v>91</v>
       </c>
@@ -20420,7 +20427,7 @@
       <c r="B150" t="s">
         <v>291</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C150" s="6" t="s">
         <v>399</v>
       </c>
       <c r="D150" t="s">
@@ -20514,7 +20521,7 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="AH150" s="6">
+      <c r="AH150" s="5">
         <f t="shared" si="9"/>
         <v>91</v>
       </c>
@@ -20537,7 +20544,7 @@
       <c r="B151" t="s">
         <v>291</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C151" s="6" t="s">
         <v>400</v>
       </c>
       <c r="D151" t="s">
@@ -20631,7 +20638,7 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="AH151" s="6">
+      <c r="AH151" s="5">
         <f t="shared" si="9"/>
         <v>91</v>
       </c>
@@ -20654,7 +20661,7 @@
       <c r="B152" t="s">
         <v>291</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C152" s="6" t="s">
         <v>401</v>
       </c>
       <c r="D152" t="s">
@@ -20748,7 +20755,7 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="AH152" s="6">
+      <c r="AH152" s="5">
         <f t="shared" si="9"/>
         <v>91</v>
       </c>
@@ -20865,7 +20872,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH153" s="6" t="str">
+      <c r="AH153" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -20873,7 +20880,7 @@
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="AJ153" s="7" t="str">
+      <c r="AJ153" s="6" t="str">
         <f t="shared" si="11"/>
         <v>JSP_mid_south_2</v>
       </c>
@@ -20985,7 +20992,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH154" s="6" t="str">
+      <c r="AH154" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -20993,7 +21000,7 @@
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="AJ154" s="7" t="str">
+      <c r="AJ154" s="6" t="str">
         <f t="shared" si="11"/>
         <v>JSP_mid_south_2</v>
       </c>
@@ -21105,7 +21112,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH155" s="6" t="str">
+      <c r="AH155" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -21113,7 +21120,7 @@
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="AJ155" s="7" t="str">
+      <c r="AJ155" s="6" t="str">
         <f t="shared" si="11"/>
         <v>JSP_mid_south_2</v>
       </c>
@@ -21225,7 +21232,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH156" s="6" t="str">
+      <c r="AH156" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -21233,7 +21240,7 @@
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="AJ156" s="7" t="str">
+      <c r="AJ156" s="6" t="str">
         <f t="shared" si="11"/>
         <v>JSP_mid_south_2</v>
       </c>
@@ -21345,7 +21352,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH157" s="6" t="str">
+      <c r="AH157" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -21462,7 +21469,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH158" s="6" t="str">
+      <c r="AH158" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -21576,7 +21583,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH159" s="6" t="str">
+      <c r="AH159" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -21693,7 +21700,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH160" s="6" t="str">
+      <c r="AH160" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -21810,7 +21817,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH161" s="6" t="str">
+      <c r="AH161" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -21927,7 +21934,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH162" s="6" t="str">
+      <c r="AH162" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -22044,7 +22051,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH163" s="6" t="str">
+      <c r="AH163" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -22161,7 +22168,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH164" s="6" t="str">
+      <c r="AH164" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -22278,7 +22285,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH165" s="6" t="str">
+      <c r="AH165" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -22392,7 +22399,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH166" s="6" t="str">
+      <c r="AH166" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -22506,7 +22513,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH167" s="6" t="str">
+      <c r="AH167" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -22620,7 +22627,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH168" s="6" t="str">
+      <c r="AH168" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -22734,7 +22741,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH169" s="6" t="str">
+      <c r="AH169" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -22848,7 +22855,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH170" s="6" t="str">
+      <c r="AH170" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -22962,7 +22969,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH171" s="6" t="str">
+      <c r="AH171" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -23076,7 +23083,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH172" s="6" t="str">
+      <c r="AH172" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -23190,7 +23197,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH173" s="6" t="str">
+      <c r="AH173" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -23304,7 +23311,7 @@
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="AH174" s="6">
+      <c r="AH174" s="5">
         <f t="shared" si="9"/>
         <v>113</v>
       </c>
@@ -23421,7 +23428,7 @@
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="AH175" s="6">
+      <c r="AH175" s="5">
         <f t="shared" si="9"/>
         <v>113</v>
       </c>
@@ -23538,7 +23545,7 @@
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="AH176" s="6">
+      <c r="AH176" s="5">
         <f t="shared" si="9"/>
         <v>114</v>
       </c>
@@ -23655,7 +23662,7 @@
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="AH177" s="6">
+      <c r="AH177" s="5">
         <f t="shared" si="9"/>
         <v>114</v>
       </c>
@@ -23772,7 +23779,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH178" s="6" t="str">
+      <c r="AH178" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -23886,7 +23893,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH179" s="6" t="str">
+      <c r="AH179" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -24000,7 +24007,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH180" s="6" t="str">
+      <c r="AH180" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -24114,7 +24121,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH181" s="6" t="str">
+      <c r="AH181" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -24228,7 +24235,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH182" s="6" t="str">
+      <c r="AH182" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -24342,7 +24349,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH183" s="6" t="str">
+      <c r="AH183" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -24456,7 +24463,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH184" s="6" t="str">
+      <c r="AH184" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -24464,7 +24471,7 @@
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="AJ184" s="7" t="str">
+      <c r="AJ184" s="6" t="str">
         <f t="shared" si="11"/>
         <v>MCN_still_2</v>
       </c>
@@ -24573,7 +24580,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH185" s="6" t="str">
+      <c r="AH185" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -24581,7 +24588,7 @@
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="AJ185" s="7" t="str">
+      <c r="AJ185" s="6" t="str">
         <f t="shared" si="11"/>
         <v>MCN_still_2</v>
       </c>
@@ -24690,7 +24697,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH186" s="6" t="str">
+      <c r="AH186" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -24804,7 +24811,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH187" s="6" t="str">
+      <c r="AH187" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -24918,7 +24925,7 @@
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="AH188" s="6">
+      <c r="AH188" s="5">
         <f t="shared" si="9"/>
         <v>125</v>
       </c>
@@ -25035,7 +25042,7 @@
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="AH189" s="6">
+      <c r="AH189" s="5">
         <f t="shared" si="9"/>
         <v>125</v>
       </c>
@@ -25152,7 +25159,7 @@
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="AH190" s="6">
+      <c r="AH190" s="5">
         <f t="shared" si="9"/>
         <v>126</v>
       </c>
@@ -25269,7 +25276,7 @@
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="AH191" s="6">
+      <c r="AH191" s="5">
         <f t="shared" si="9"/>
         <v>126</v>
       </c>
@@ -25386,7 +25393,7 @@
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="AH192" s="6">
+      <c r="AH192" s="5">
         <f t="shared" si="9"/>
         <v>127</v>
       </c>
@@ -25503,7 +25510,7 @@
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="AH193" s="6">
+      <c r="AH193" s="5">
         <f t="shared" si="9"/>
         <v>127</v>
       </c>
@@ -25620,7 +25627,7 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="AH194" s="6" t="str">
+      <c r="AH194" s="5" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -25734,7 +25741,7 @@
         <f t="shared" ref="AG195:AG258" si="12">COUNTIF(AF:AF,AF195)</f>
         <v>1</v>
       </c>
-      <c r="AH195" s="6" t="str">
+      <c r="AH195" s="5" t="str">
         <f t="shared" ref="AH195:AH258" si="13">IF(AG195&gt;1,AF195,"")</f>
         <v/>
       </c>
@@ -25848,7 +25855,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH196" s="6" t="str">
+      <c r="AH196" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -25856,7 +25863,7 @@
         <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="AJ196" s="7" t="str">
+      <c r="AJ196" s="6" t="str">
         <f t="shared" si="15"/>
         <v>MRE_1</v>
       </c>
@@ -25968,7 +25975,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH197" s="6" t="str">
+      <c r="AH197" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -25976,7 +25983,7 @@
         <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="AJ197" s="7" t="str">
+      <c r="AJ197" s="6" t="str">
         <f t="shared" si="15"/>
         <v>MRE_1</v>
       </c>
@@ -26085,7 +26092,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH198" s="6" t="str">
+      <c r="AH198" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -26093,11 +26100,11 @@
         <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="AJ198" s="7" t="str">
+      <c r="AJ198" s="6" t="str">
         <f t="shared" si="15"/>
         <v>MRE_2</v>
       </c>
-      <c r="AK198" s="9" t="s">
+      <c r="AK198" s="8" t="s">
         <v>704</v>
       </c>
     </row>
@@ -26202,7 +26209,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH199" s="6" t="str">
+      <c r="AH199" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -26210,11 +26217,11 @@
         <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="AJ199" s="7" t="str">
+      <c r="AJ199" s="6" t="str">
         <f t="shared" si="15"/>
         <v>MRE_2</v>
       </c>
-      <c r="AK199" s="9" t="s">
+      <c r="AK199" s="8" t="s">
         <v>704</v>
       </c>
     </row>
@@ -26319,7 +26326,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH200" s="6" t="str">
+      <c r="AH200" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -26433,7 +26440,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH201" s="6" t="str">
+      <c r="AH201" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -26547,7 +26554,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH202" s="6" t="str">
+      <c r="AH202" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -26661,7 +26668,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH203" s="6" t="str">
+      <c r="AH203" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -26775,7 +26782,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH204" s="6" t="str">
+      <c r="AH204" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -26889,7 +26896,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH205" s="6" t="str">
+      <c r="AH205" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -27003,7 +27010,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH206" s="6" t="str">
+      <c r="AH206" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -27117,7 +27124,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH207" s="6" t="str">
+      <c r="AH207" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -27231,7 +27238,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH208" s="6" t="str">
+      <c r="AH208" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -27345,7 +27352,7 @@
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="AH209" s="6">
+      <c r="AH209" s="5">
         <f t="shared" si="13"/>
         <v>143</v>
       </c>
@@ -27462,7 +27469,7 @@
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="AH210" s="6">
+      <c r="AH210" s="5">
         <f t="shared" si="13"/>
         <v>143</v>
       </c>
@@ -27579,7 +27586,7 @@
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="AH211" s="6">
+      <c r="AH211" s="5">
         <f t="shared" si="13"/>
         <v>143</v>
       </c>
@@ -27696,7 +27703,7 @@
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="AH212" s="6">
+      <c r="AH212" s="5">
         <f t="shared" si="13"/>
         <v>143</v>
       </c>
@@ -27813,7 +27820,7 @@
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="AH213" s="6">
+      <c r="AH213" s="5">
         <f t="shared" si="13"/>
         <v>144</v>
       </c>
@@ -27930,7 +27937,7 @@
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="AH214" s="6">
+      <c r="AH214" s="5">
         <f t="shared" si="13"/>
         <v>144</v>
       </c>
@@ -28047,7 +28054,7 @@
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="AH215" s="6">
+      <c r="AH215" s="5">
         <f t="shared" si="13"/>
         <v>144</v>
       </c>
@@ -28164,7 +28171,7 @@
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="AH216" s="6">
+      <c r="AH216" s="5">
         <f t="shared" si="13"/>
         <v>144</v>
       </c>
@@ -28281,7 +28288,7 @@
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="AH217" s="6">
+      <c r="AH217" s="5">
         <f t="shared" si="13"/>
         <v>145</v>
       </c>
@@ -28398,7 +28405,7 @@
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="AH218" s="6">
+      <c r="AH218" s="5">
         <f t="shared" si="13"/>
         <v>145</v>
       </c>
@@ -28515,7 +28522,7 @@
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="AH219" s="6">
+      <c r="AH219" s="5">
         <f t="shared" si="13"/>
         <v>145</v>
       </c>
@@ -28632,7 +28639,7 @@
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="AH220" s="6">
+      <c r="AH220" s="5">
         <f t="shared" si="13"/>
         <v>145</v>
       </c>
@@ -28749,7 +28756,7 @@
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="AH221" s="6">
+      <c r="AH221" s="5">
         <f t="shared" si="13"/>
         <v>146</v>
       </c>
@@ -28866,7 +28873,7 @@
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="AH222" s="6">
+      <c r="AH222" s="5">
         <f t="shared" si="13"/>
         <v>146</v>
       </c>
@@ -28983,7 +28990,7 @@
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="AH223" s="6">
+      <c r="AH223" s="5">
         <f t="shared" si="13"/>
         <v>146</v>
       </c>
@@ -29100,7 +29107,7 @@
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="AH224" s="6">
+      <c r="AH224" s="5">
         <f t="shared" si="13"/>
         <v>146</v>
       </c>
@@ -29217,7 +29224,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH225" s="6" t="str">
+      <c r="AH225" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -29331,7 +29338,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH226" s="6" t="str">
+      <c r="AH226" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -29445,7 +29452,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH227" s="6" t="str">
+      <c r="AH227" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -29453,7 +29460,7 @@
         <f t="shared" si="14"/>
         <v>6</v>
       </c>
-      <c r="AJ227" s="7" t="str">
+      <c r="AJ227" s="6" t="str">
         <f t="shared" si="15"/>
         <v>QMH_4S</v>
       </c>
@@ -29562,7 +29569,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH228" s="6" t="str">
+      <c r="AH228" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -29676,7 +29683,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH229" s="6" t="str">
+      <c r="AH229" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -29790,7 +29797,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH230" s="6" t="str">
+      <c r="AH230" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -29904,7 +29911,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH231" s="6" t="str">
+      <c r="AH231" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -30018,7 +30025,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH232" s="6" t="str">
+      <c r="AH232" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -30132,7 +30139,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH233" s="6" t="str">
+      <c r="AH233" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -30246,7 +30253,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH234" s="6" t="str">
+      <c r="AH234" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -30254,7 +30261,7 @@
         <f t="shared" si="14"/>
         <v>6</v>
       </c>
-      <c r="AJ234" s="7" t="str">
+      <c r="AJ234" s="6" t="str">
         <f t="shared" si="15"/>
         <v>QMH_4S</v>
       </c>
@@ -30363,7 +30370,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH235" s="6" t="str">
+      <c r="AH235" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -30371,7 +30378,7 @@
         <f t="shared" si="14"/>
         <v>6</v>
       </c>
-      <c r="AJ235" s="7" t="str">
+      <c r="AJ235" s="6" t="str">
         <f t="shared" si="15"/>
         <v>QMH_4S</v>
       </c>
@@ -30480,7 +30487,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH236" s="6" t="str">
+      <c r="AH236" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -30488,7 +30495,7 @@
         <f t="shared" si="14"/>
         <v>6</v>
       </c>
-      <c r="AJ236" s="7" t="str">
+      <c r="AJ236" s="6" t="str">
         <f t="shared" si="15"/>
         <v>QMH_4S</v>
       </c>
@@ -30597,7 +30604,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH237" s="6" t="str">
+      <c r="AH237" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -30605,7 +30612,7 @@
         <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="AJ237" s="7" t="str">
+      <c r="AJ237" s="6" t="str">
         <f t="shared" si="15"/>
         <v>QMH_5a</v>
       </c>
@@ -30714,7 +30721,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH238" s="6" t="str">
+      <c r="AH238" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -30722,7 +30729,7 @@
         <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="AJ238" s="7" t="str">
+      <c r="AJ238" s="6" t="str">
         <f t="shared" si="15"/>
         <v>QMH_5a</v>
       </c>
@@ -30831,7 +30838,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH239" s="6" t="str">
+      <c r="AH239" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -30839,7 +30846,7 @@
         <f t="shared" si="14"/>
         <v>6</v>
       </c>
-      <c r="AJ239" s="7" t="str">
+      <c r="AJ239" s="6" t="str">
         <f t="shared" si="15"/>
         <v>QMH_4S</v>
       </c>
@@ -30948,7 +30955,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH240" s="6" t="str">
+      <c r="AH240" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -30956,7 +30963,7 @@
         <f t="shared" si="14"/>
         <v>6</v>
       </c>
-      <c r="AJ240" s="7" t="str">
+      <c r="AJ240" s="6" t="str">
         <f t="shared" si="15"/>
         <v>QMH_4S</v>
       </c>
@@ -31065,7 +31072,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH241" s="6" t="str">
+      <c r="AH241" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -31179,7 +31186,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH242" s="6" t="str">
+      <c r="AH242" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -31293,7 +31300,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH243" s="6" t="str">
+      <c r="AH243" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -31407,7 +31414,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH244" s="6" t="str">
+      <c r="AH244" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -31521,7 +31528,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH245" s="6" t="str">
+      <c r="AH245" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -31635,7 +31642,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH246" s="6" t="str">
+      <c r="AH246" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -31749,7 +31756,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH247" s="6" t="str">
+      <c r="AH247" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -31863,7 +31870,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH248" s="6" t="str">
+      <c r="AH248" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -31977,7 +31984,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH249" s="6" t="str">
+      <c r="AH249" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -32091,7 +32098,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH250" s="6" t="str">
+      <c r="AH250" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -32205,7 +32212,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH251" s="6" t="str">
+      <c r="AH251" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -32319,7 +32326,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH252" s="6" t="str">
+      <c r="AH252" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -32433,7 +32440,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH253" s="6" t="str">
+      <c r="AH253" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -32547,7 +32554,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH254" s="6" t="str">
+      <c r="AH254" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -32661,7 +32668,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH255" s="6" t="str">
+      <c r="AH255" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -32775,7 +32782,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AH256" s="6" t="str">
+      <c r="AH256" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -32889,7 +32896,7 @@
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="AH257" s="6">
+      <c r="AH257" s="5">
         <f t="shared" si="13"/>
         <v>179</v>
       </c>
@@ -33006,7 +33013,7 @@
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="AH258" s="6">
+      <c r="AH258" s="5">
         <f t="shared" si="13"/>
         <v>179</v>
       </c>
@@ -33123,7 +33130,7 @@
         <f t="shared" ref="AG259:AG277" si="16">COUNTIF(AF:AF,AF259)</f>
         <v>1</v>
       </c>
-      <c r="AH259" s="6" t="str">
+      <c r="AH259" s="5" t="str">
         <f t="shared" ref="AH259:AH277" si="17">IF(AG259&gt;1,AF259,"")</f>
         <v/>
       </c>
@@ -33237,7 +33244,7 @@
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="AH260" s="6" t="str">
+      <c r="AH260" s="5" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -33351,7 +33358,7 @@
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="AH261" s="6" t="str">
+      <c r="AH261" s="5" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -33465,7 +33472,7 @@
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="AH262" s="6" t="str">
+      <c r="AH262" s="5" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -33579,7 +33586,7 @@
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="AH263" s="6" t="str">
+      <c r="AH263" s="5" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -33693,7 +33700,7 @@
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="AH264" s="6" t="str">
+      <c r="AH264" s="5" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -33807,7 +33814,7 @@
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="AH265" s="6" t="str">
+      <c r="AH265" s="5" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -33815,7 +33822,7 @@
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
-      <c r="AJ265" s="7" t="str">
+      <c r="AJ265" s="6" t="str">
         <f t="shared" si="19"/>
         <v>WES_test_1</v>
       </c>
@@ -33924,7 +33931,7 @@
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="AH266" s="6" t="str">
+      <c r="AH266" s="5" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -33932,7 +33939,7 @@
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
-      <c r="AJ266" s="7" t="str">
+      <c r="AJ266" s="6" t="str">
         <f t="shared" si="19"/>
         <v>WES_test_1</v>
       </c>
@@ -34041,7 +34048,7 @@
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="AH267" s="6" t="str">
+      <c r="AH267" s="5" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -34049,7 +34056,7 @@
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
-      <c r="AJ267" s="7" t="str">
+      <c r="AJ267" s="6" t="str">
         <f t="shared" si="19"/>
         <v>WES_test_1</v>
       </c>
@@ -34158,7 +34165,7 @@
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="AH268" s="6" t="str">
+      <c r="AH268" s="5" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -34166,7 +34173,7 @@
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
-      <c r="AJ268" s="7" t="str">
+      <c r="AJ268" s="6" t="str">
         <f t="shared" si="19"/>
         <v>WES_test_1</v>
       </c>
@@ -34259,7 +34266,7 @@
       <c r="AB269">
         <v>122.222222222222</v>
       </c>
-      <c r="AC269" t="s">
+      <c r="AC269" s="8" t="s">
         <v>120</v>
       </c>
       <c r="AD269" t="s">
@@ -34275,7 +34282,7 @@
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="AH269" s="6" t="str">
+      <c r="AH269" s="5" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -34283,7 +34290,7 @@
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
-      <c r="AJ269" s="7" t="str">
+      <c r="AJ269" s="6" t="str">
         <f t="shared" si="19"/>
         <v>WES_test_1</v>
       </c>
@@ -34395,7 +34402,7 @@
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="AH270" s="6" t="str">
+      <c r="AH270" s="5" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -34509,7 +34516,7 @@
         <f t="shared" si="16"/>
         <v>4</v>
       </c>
-      <c r="AH271" s="6">
+      <c r="AH271" s="5">
         <f t="shared" si="17"/>
         <v>192</v>
       </c>
@@ -34626,7 +34633,7 @@
         <f t="shared" si="16"/>
         <v>4</v>
       </c>
-      <c r="AH272" s="6">
+      <c r="AH272" s="5">
         <f t="shared" si="17"/>
         <v>192</v>
       </c>
@@ -34743,7 +34750,7 @@
         <f t="shared" si="16"/>
         <v>4</v>
       </c>
-      <c r="AH273" s="6">
+      <c r="AH273" s="5">
         <f t="shared" si="17"/>
         <v>192</v>
       </c>
@@ -34860,7 +34867,7 @@
         <f t="shared" si="16"/>
         <v>4</v>
       </c>
-      <c r="AH274" s="6">
+      <c r="AH274" s="5">
         <f t="shared" si="17"/>
         <v>192</v>
       </c>
@@ -34977,7 +34984,7 @@
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="AH275" s="6" t="str">
+      <c r="AH275" s="5" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -35091,7 +35098,7 @@
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="AH276" s="6" t="str">
+      <c r="AH276" s="5" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -35205,7 +35212,7 @@
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="AH277" s="6" t="str">
+      <c r="AH277" s="5" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -35219,84 +35226,84 @@
       </c>
     </row>
     <row r="278" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AH278" s="6"/>
+      <c r="AH278" s="5"/>
       <c r="AJ278" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="279" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AH279" s="6"/>
+      <c r="AH279" s="5"/>
       <c r="AJ279" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="280" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AH280" s="6"/>
+      <c r="AH280" s="5"/>
       <c r="AJ280" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="281" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AH281" s="6"/>
+      <c r="AH281" s="5"/>
       <c r="AJ281" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="282" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AH282" s="6"/>
+      <c r="AH282" s="5"/>
       <c r="AJ282" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="283" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AH283" s="6"/>
+      <c r="AH283" s="5"/>
       <c r="AJ283" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="284" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AH284" s="6"/>
+      <c r="AH284" s="5"/>
       <c r="AJ284" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="285" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AH285" s="6"/>
+      <c r="AH285" s="5"/>
       <c r="AJ285" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="286" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AH286" s="6"/>
+      <c r="AH286" s="5"/>
       <c r="AJ286" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="287" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AH287" s="6"/>
+      <c r="AH287" s="5"/>
       <c r="AJ287" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="288" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AH288" s="6"/>
+      <c r="AH288" s="5"/>
       <c r="AJ288" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="289" spans="34:36" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AH289" s="6"/>
+      <c r="AH289" s="5"/>
       <c r="AJ289" t="str">
         <f t="shared" si="19"/>
         <v/>
